--- a/固件/IP2366固件/IP2366_I2C_140W_2M50_REG.xlsx
+++ b/固件/IP2366固件/IP2366_I2C_140W_2M50_REG.xlsx
@@ -73,6 +73,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_LOADOTP</t>
     </r>
     <r>
@@ -102,6 +110,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">EN_MCURST
 </t>
     </r>
@@ -118,6 +134,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_INT_low</t>
     </r>
     <r>
@@ -136,26 +160,14 @@
   </si>
   <si>
     <r>
-      <t>En_Vbus_SinkDPDM</t>
-    </r>
-    <r>
-      <rPr>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>连接适配器对电池充电时是否尝试握手基于USB数据线协商的快充协议</t>
+      <t>En_Vbus_SinkDPDM</t>
     </r>
     <r>
       <rPr>
@@ -164,7 +176,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>(QC AFC</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -173,7 +186,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>之类</t>
+      <t>连接适配器对电池充电时是否尝试握手基于USB数据线协商的快充协议</t>
     </r>
     <r>
       <rPr>
@@ -182,8 +195,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>)
-1</t>
+      <t>(QC AFC</t>
     </r>
     <r>
       <rPr>
@@ -192,7 +204,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：尝试协商</t>
+      <t>之类</t>
     </r>
     <r>
       <rPr>
@@ -201,8 +213,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-0</t>
+      <t>)
+1</t>
     </r>
     <r>
       <rPr>
@@ -211,12 +223,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：禁用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>En _Vbus_SinkPd</t>
+      <t>：尝试协商</t>
     </r>
     <r>
       <rPr>
@@ -226,7 +233,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-</t>
+0</t>
     </r>
     <r>
       <rPr>
@@ -235,25 +242,19 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>连接适配器对电池充电时是否尝试握手</t>
-    </r>
-    <r>
-      <rPr>
+      <t>：禁用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve"> PD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>协议快充（包括PD FIXED和PPS以及EPR AVS）</t>
+      <t>En _Vbus_SinkPd</t>
     </r>
     <r>
       <rPr>
@@ -263,7 +264,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-1</t>
+</t>
     </r>
     <r>
       <rPr>
@@ -272,7 +273,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：尝试PD协商</t>
+      <t>连接适配器对电池充电时是否尝试握手</t>
     </r>
     <r>
       <rPr>
@@ -281,8 +282,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-0</t>
+      <t xml:space="preserve"> PD</t>
     </r>
     <r>
       <rPr>
@@ -291,12 +291,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：禁用</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>En_Vbus_SinkSCP</t>
+      <t>协议快充（包括PD FIXED和PPS以及EPR AVS）</t>
     </r>
     <r>
       <rPr>
@@ -306,7 +301,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-</t>
+1</t>
     </r>
     <r>
       <rPr>
@@ -315,7 +310,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>连接适配器对电池充电时是否尝试握手华为SCP和HSCP协议</t>
+      <t>：尝试PD协商</t>
     </r>
     <r>
       <rPr>
@@ -325,7 +320,7 @@
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
-1</t>
+0</t>
     </r>
     <r>
       <rPr>
@@ -334,26 +329,19 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>：尝试SCP和HSCP</t>
-    </r>
-    <r>
-      <rPr>
+      <t>：禁用</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>：</t>
+      <t>En_Vbus_SinkSCP</t>
     </r>
     <r>
       <rPr>
@@ -362,6 +350,63 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>连接适配器对电池充电时是否尝试握手华为SCP和HSCP协议</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：尝试SCP和HSCP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>disable</t>
     </r>
   </si>
@@ -370,6 +415,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En Charger
 是否允许系统执行充电流程对电池进行充电。</t>
     </r>
@@ -401,6 +453,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>绿色</t>
     </r>
     <r>
@@ -531,6 +591,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">VSET_FULL[7:0]
 </t>
     </r>
@@ -556,6 +624,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IBAT_PEAK_MAXIMUM[7:0]</t>
     </r>
     <r>
@@ -581,6 +657,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IBAT_PRECHARGE_RMS[7:0]</t>
     </r>
     <r>
@@ -606,6 +690,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>IStop[3:0]</t>
     </r>
     <r>
@@ -644,6 +736,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VRecharge[1:0]</t>
     </r>
     <r>
@@ -673,6 +773,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>EN_SYS_Standby</t>
     </r>
     <r>
@@ -691,6 +799,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Enter_Standby</t>
     </r>
     <r>
@@ -727,6 +843,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>EN_5V_UVLO</t>
     </r>
     <r>
@@ -752,6 +876,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VBAT_LOW_Thres[2:0]</t>
     </r>
     <r>
@@ -800,6 +932,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>EN_DCDC_OUTPUT</t>
     </r>
     <r>
@@ -818,6 +958,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">En_Vbus_Src_DPDM
 </t>
     </r>
@@ -836,6 +984,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Vbus_Src_PD</t>
     </r>
     <r>
@@ -854,6 +1010,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En _Vbus_SrcSCP</t>
     </r>
     <r>
@@ -881,6 +1045,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_MAX_POWER[2:0]</t>
     </r>
     <r>
@@ -926,6 +1098,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>INPUT_PDO_SEL[2:0]
 当系统连接PD适配器时，选择输入握手的 PD Fixed档位（</t>
     </r>
@@ -973,6 +1152,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_CC_MODE[1:0]</t>
     </r>
     <r>
@@ -1019,6 +1206,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5V_DEFAULT_ISET</t>
     </r>
     <r>
@@ -1036,6 +1231,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PPS2_PDO_ISource</t>
     </r>
     <r>
@@ -1054,6 +1257,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PPS1_PDO_ISource</t>
     </r>
     <r>
@@ -1072,6 +1283,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>20VPDO_ISource</t>
     </r>
     <r>
@@ -1090,6 +1309,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>15VPDO_ISource</t>
     </r>
     <r>
@@ -1108,6 +1335,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12VPDO_ISource</t>
     </r>
     <r>
@@ -1126,6 +1361,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>9VPDO_ISource</t>
     </r>
     <r>
@@ -1144,6 +1387,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5VPDO_ISource</t>
     </r>
     <r>
@@ -1168,6 +1419,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5V_PDO_ISET[7:0]</t>
     </r>
     <r>
@@ -1193,6 +1452,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>9V_PDO_ISET[7:0]</t>
     </r>
     <r>
@@ -1215,6 +1482,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>12V_PDO_ISET[7:0]</t>
     </r>
     <r>
@@ -1237,6 +1512,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>15V_PDO_ISET[7:0]</t>
     </r>
     <r>
@@ -1259,6 +1542,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>20V_PDO_ISET[7:0]</t>
     </r>
     <r>
@@ -1284,6 +1575,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_Pps2Pdo</t>
     </r>
     <r>
@@ -1301,6 +1600,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_Pps1Pdo</t>
     </r>
     <r>
@@ -1318,6 +1625,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_20VPdo</t>
     </r>
     <r>
@@ -1335,6 +1650,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_15VPdo</t>
     </r>
     <r>
@@ -1352,6 +1675,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_12VPdo</t>
     </r>
     <r>
@@ -1369,6 +1700,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>En_Src_9VPdo</t>
     </r>
     <r>
@@ -1395,6 +1734,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">15VPDO_ADD10mA
 </t>
     </r>
@@ -1413,6 +1760,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">12VPDO_ADD10mA
 </t>
     </r>
@@ -1431,6 +1786,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">9VPDO_ADD10mA
 </t>
     </r>
@@ -1449,6 +1812,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>5VPDO_ADD10mA</t>
     </r>
     <r>
@@ -1473,6 +1844,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">PPS1_PDO_ISET[6:0]
 </t>
     </r>
@@ -1499,6 +1878,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">PPS2_PDO_ISET[6:0]
 </t>
     </r>
@@ -1516,6 +1903,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">IP2366 2M50 140W 3S Special Firmware Register Map
 Created By: </t>
     </r>
@@ -1556,6 +1951,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>CHG_EN</t>
     </r>
     <r>
@@ -1572,6 +1975,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>CHG_End</t>
     </r>
     <r>
@@ -1588,6 +1999,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Output_En</t>
     </r>
     <r>
@@ -1604,6 +2023,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Charging_State[2:0]</t>
     </r>
     <r>
@@ -1623,6 +2050,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF92D050"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>绿色</t>
     </r>
     <r>
@@ -1699,6 +2134,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>HV_Charge_Enabled[1:0]</t>
     </r>
     <r>
@@ -1722,6 +2165,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Vbus_Ok</t>
     </r>
     <r>
@@ -1739,6 +2190,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Vbus_OV</t>
     </r>
     <r>
@@ -1756,6 +2215,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Selected_PDO[2:0]</t>
     </r>
     <r>
@@ -1792,7 +2258,28 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">指示系统对外输出时是否进入过流保护状态。
+      <t>指示系统对外输出时是否进入</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>过流保护</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">状态。
 0:未进入 1:进入
 </t>
     </r>
@@ -1820,7 +2307,26 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>指示系统对外输出时是否进入过流保护状态。
+      <t>指示系统对外输出时是否进入</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>短路保护</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>状态。
 0:未进入 1:进入</t>
     </r>
     <r>
@@ -1855,6 +2361,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Sink_Ok</t>
     </r>
     <r>
@@ -1871,6 +2385,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Src_Ok</t>
     </r>
     <r>
@@ -1888,6 +2410,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Src_Pd_Ok</t>
     </r>
     <r>
@@ -1905,6 +2435,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Sink_Pd_Ok</t>
     </r>
     <r>
@@ -1921,26 +2459,14 @@
   </si>
   <si>
     <r>
-      <t>Vbus_Sink_Qc_Ok</t>
-    </r>
-    <r>
-      <rPr>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>指示芯片和</t>
+      <t>Vbus_Sink_Qc_Ok</t>
     </r>
     <r>
       <rPr>
@@ -1949,7 +2475,8 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>Type-C</t>
+      <t xml:space="preserve">
+</t>
     </r>
     <r>
       <rPr>
@@ -1958,7 +2485,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>所连接的供电设备之间是否成功协商快充</t>
+      <t>指示芯片和</t>
     </r>
     <r>
       <rPr>
@@ -1967,8 +2494,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">
-1:</t>
+      <t>Type-C</t>
     </r>
     <r>
       <rPr>
@@ -1977,11 +2503,38 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
+      <t>所连接的供电设备之间是否成功协商快充</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>已连接</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Vbus_Src_Qc_Ok</t>
     </r>
     <r>
@@ -2005,6 +2558,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PDO_20V_PRESENT</t>
     </r>
     <r>
@@ -2022,6 +2583,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PDO_15V_PRESENT</t>
     </r>
     <r>
@@ -2039,6 +2608,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PDO_12V_PRESENT</t>
     </r>
     <r>
@@ -2056,6 +2633,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PDO_9V_PRESENT</t>
     </r>
     <r>
@@ -2073,6 +2658,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>PDO_5V_PRESENT</t>
     </r>
     <r>
@@ -2096,6 +2689,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VBAT_PIN_VOLTAGE[7:0]</t>
     </r>
     <r>
@@ -2118,6 +2719,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VBAT_PIN_VOLTAGE[15:8]</t>
     </r>
     <r>
@@ -2205,6 +2814,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VTYPEC_PIN_VOLTAGE[7:0]</t>
     </r>
     <r>
@@ -2227,6 +2844,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VTYPEC_PIN_VOLTAGE[15:8]</t>
     </r>
     <r>
@@ -2314,6 +2939,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>BATTERY_CURRENT[7:0]</t>
     </r>
     <r>
@@ -2336,6 +2969,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>BATTERY_CURRENT[15:8]</t>
     </r>
     <r>
@@ -2455,6 +3096,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_CURRENT[7:0]</t>
     </r>
     <r>
@@ -2477,6 +3126,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_CURRENT[15:8]</t>
     </r>
     <r>
@@ -2596,6 +3253,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_POWER[7:0]</t>
     </r>
     <r>
@@ -2618,6 +3283,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TYPEC_POWER[15:8]</t>
     </r>
     <r>
@@ -2737,6 +3410,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>NTC_IOUT_STATE</t>
     </r>
     <r>
@@ -2761,6 +3442,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VGPIO0_NTC_VOLTAGE[7:0]</t>
     </r>
     <r>
@@ -2783,6 +3472,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>VGPIO0_NTC_VOLTAGE[15:8]</t>
     </r>
     <r>
@@ -2859,6 +3556,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MFR_FIRMWARE_TIMESTAMP0[7:0]</t>
     </r>
     <r>
@@ -2881,6 +3586,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MFR_FIRMWARE_TIMESTAMP1[7:0]</t>
     </r>
     <r>
@@ -2903,6 +3616,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MFR_FIRMWARE_TIMESTAMP2[7:0]</t>
     </r>
     <r>
@@ -2925,6 +3646,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MFR_FIRMWARE_TIMESTAMP3[7:0]</t>
     </r>
     <r>
@@ -2947,6 +3676,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>MFR_FIRMWARE_TIMESTAMP4[7:0]</t>
     </r>
     <r>
@@ -3177,8 +3914,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFC00000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3186,7 +3931,52 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFF00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Blackadder ITC"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3222,61 +4012,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Blackadder ITC"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="39">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3298,12 +4035,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3769,7 +4500,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3793,16 +4524,16 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -3811,89 +4542,89 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3945,9 +4676,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3957,9 +4685,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3969,10 +4694,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3993,76 +4718,76 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4438,7 +5163,7 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="25" t="s">
+      <c r="M1" s="23" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4452,31 +5177,31 @@
       <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="33" t="s">
+      <c r="D2" s="31" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="52" t="s">
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="26" t="s">
+      <c r="M2" s="24" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4487,16 +5212,16 @@
       <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="37"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="35"/>
       <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
@@ -4508,16 +5233,16 @@
       <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="37"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="35"/>
       <c r="K4" s="1" t="s">
         <v>31</v>
       </c>
@@ -4529,16 +5254,16 @@
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="37"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="35"/>
       <c r="K5" s="1" t="s">
         <v>35</v>
       </c>
@@ -4550,12 +5275,12 @@
       <c r="B6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="6" t="s">
         <v>39</v>
       </c>
@@ -4578,7 +5303,7 @@
       <c r="C7" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -4605,7 +5330,7 @@
       <c r="C8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="22"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="7"/>
       <c r="F8" s="3" t="s">
         <v>20</v>
@@ -4657,7 +5382,7 @@
       <c r="C10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="22"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="7"/>
       <c r="F10" s="3" t="s">
         <v>20</v>
@@ -4684,11 +5409,11 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="38" t="s">
+      <c r="H11" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="I11" s="55"/>
-      <c r="J11" s="56"/>
+      <c r="I11" s="53"/>
+      <c r="J11" s="54"/>
       <c r="K11" s="2" t="s">
         <v>27</v>
       </c>
@@ -4761,12 +5486,12 @@
       <c r="C14" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
       <c r="J14" s="7"/>
       <c r="K14" s="1" t="s">
         <v>80</v>
@@ -4782,12 +5507,12 @@
       <c r="C15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
       <c r="J15" s="7"/>
       <c r="K15" s="1" t="s">
         <v>80</v>
@@ -4803,12 +5528,12 @@
       <c r="C16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
       <c r="J16" s="7"/>
       <c r="K16" s="1" t="s">
         <v>80</v>
@@ -4824,12 +5549,12 @@
       <c r="C17" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
       <c r="J17" s="7"/>
       <c r="K17" s="1" t="s">
         <v>80</v>
@@ -4845,12 +5570,12 @@
       <c r="C18" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
       <c r="J18" s="7"/>
       <c r="K18" s="1" t="s">
         <v>93</v>
@@ -4863,28 +5588,28 @@
       <c r="B19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="D19" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="E19" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="F19" s="40" t="s">
+      <c r="F19" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="40" t="s">
+      <c r="G19" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="40" t="s">
+      <c r="H19" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="40" t="s">
+      <c r="I19" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="J19" s="57" t="s">
+      <c r="J19" s="55" t="s">
         <v>20</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -4898,22 +5623,22 @@
       <c r="B20" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="40" t="s">
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="38" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="40" t="s">
+      <c r="H20" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="I20" s="40" t="s">
+      <c r="I20" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="J20" s="40" t="s">
+      <c r="J20" s="38" t="s">
         <v>108</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -4927,293 +5652,293 @@
       <c r="B21" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C21" s="44" t="s">
+      <c r="C21" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="58"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="56"/>
       <c r="K21" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1" spans="1:11">
-      <c r="A22" s="46" t="s">
+      <c r="A22" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="49"/>
-      <c r="I22" s="49"/>
-      <c r="J22" s="59"/>
-      <c r="K22" s="47" t="s">
+      <c r="E22" s="47"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="47"/>
+      <c r="I22" s="47"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="45" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="23" ht="115" customHeight="1" spans="1:11">
-      <c r="A23" s="50" t="s">
+      <c r="A23" s="48" t="s">
         <v>116</v>
       </c>
-      <c r="B23" s="51"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="60"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="49"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="58"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="52"/>
-      <c r="K24" s="52"/>
+      <c r="A24" s="50"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="52"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="52"/>
-      <c r="K25" s="52"/>
+      <c r="A25" s="50"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="52"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="52"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="52"/>
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="52"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
+      <c r="A29" s="50"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="52"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="52"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="52"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="52"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="50"/>
+      <c r="E36" s="50"/>
+      <c r="F36" s="50"/>
+      <c r="G36" s="50"/>
+      <c r="H36" s="50"/>
+      <c r="I36" s="50"/>
+      <c r="J36" s="50"/>
+      <c r="K36" s="50"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
+      <c r="C37" s="50"/>
+      <c r="D37" s="50"/>
+      <c r="E37" s="50"/>
+      <c r="F37" s="50"/>
+      <c r="G37" s="50"/>
+      <c r="H37" s="50"/>
+      <c r="I37" s="50"/>
+      <c r="J37" s="50"/>
+      <c r="K37" s="50"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
+      <c r="A38" s="50"/>
+      <c r="B38" s="50"/>
+      <c r="C38" s="50"/>
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="52"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
+      <c r="J39" s="50"/>
+      <c r="K39" s="50"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="52"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="50"/>
+      <c r="C40" s="50"/>
+      <c r="D40" s="50"/>
+      <c r="E40" s="50"/>
+      <c r="F40" s="50"/>
+      <c r="G40" s="50"/>
+      <c r="H40" s="50"/>
+      <c r="I40" s="50"/>
+      <c r="J40" s="50"/>
+      <c r="K40" s="50"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="52"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="52"/>
-      <c r="D41" s="52"/>
-      <c r="E41" s="52"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="52"/>
-      <c r="H41" s="52"/>
-      <c r="I41" s="52"/>
-      <c r="J41" s="52"/>
-      <c r="K41" s="52"/>
+      <c r="A41" s="50"/>
+      <c r="B41" s="50"/>
+      <c r="C41" s="50"/>
+      <c r="D41" s="50"/>
+      <c r="E41" s="50"/>
+      <c r="F41" s="50"/>
+      <c r="G41" s="50"/>
+      <c r="H41" s="50"/>
+      <c r="I41" s="50"/>
+      <c r="J41" s="50"/>
+      <c r="K41" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -5299,7 +6024,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="23" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5326,9 +6051,9 @@
       <c r="H2" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="22"/>
+      <c r="I2" s="20"/>
       <c r="J2" s="7"/>
-      <c r="L2" s="26" t="s">
+      <c r="L2" s="24" t="s">
         <v>123</v>
       </c>
     </row>
@@ -5373,8 +6098,8 @@
       <c r="H4" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="26"/>
     </row>
     <row r="5" ht="119" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
@@ -5390,14 +6115,14 @@
       <c r="E5" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="16" t="s">
         <v>135</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
       <c r="J5" s="15"/>
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:10">
@@ -5407,28 +6132,28 @@
       <c r="B6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="30"/>
+      <c r="J6" s="28"/>
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
@@ -5445,16 +6170,16 @@
       <c r="F7" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="5" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5468,12 +6193,12 @@
       <c r="C8" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="7"/>
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:10">
@@ -5486,12 +6211,12 @@
       <c r="C9" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
       <c r="J9" s="7"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:10">
@@ -5504,12 +6229,12 @@
       <c r="C10" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
       <c r="J10" s="7"/>
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:10">
@@ -5522,12 +6247,12 @@
       <c r="C11" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
       <c r="J11" s="7"/>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:10">
@@ -5540,12 +6265,12 @@
       <c r="C12" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
       <c r="J12" s="7"/>
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:10">
@@ -5558,12 +6283,12 @@
       <c r="C13" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
       <c r="J13" s="7"/>
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:10">
@@ -5576,12 +6301,12 @@
       <c r="C14" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
       <c r="J14" s="7"/>
     </row>
     <row r="15" ht="76" customHeight="1" spans="1:10">
@@ -5594,12 +6319,12 @@
       <c r="C15" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" ht="31" customHeight="1" spans="1:10">
@@ -5612,13 +6337,13 @@
       <c r="C16" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="31"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="29"/>
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:10">
       <c r="A17" s="2" t="s">
@@ -5630,12 +6355,12 @@
       <c r="C17" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
       <c r="J17" s="7"/>
     </row>
     <row r="18" ht="86.4" spans="1:10">
@@ -5668,12 +6393,12 @@
       <c r="C19" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="D19" s="22"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
       <c r="J19" s="7"/>
     </row>
     <row r="20" ht="65" customHeight="1" spans="1:10">
@@ -5686,12 +6411,12 @@
       <c r="C20" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
       <c r="J20" s="7"/>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:10">
@@ -5704,12 +6429,12 @@
       <c r="C21" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
       <c r="J21" s="7"/>
     </row>
     <row r="22" ht="29" customHeight="1" spans="1:10">
@@ -5722,12 +6447,12 @@
       <c r="C22" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
       <c r="J22" s="7"/>
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:10">
@@ -5740,13 +6465,13 @@
       <c r="C23" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="31"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="29"/>
     </row>
     <row r="24" ht="37" customHeight="1" spans="1:10">
       <c r="A24" s="2" t="s">
@@ -5758,12 +6483,12 @@
       <c r="C24" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
       <c r="J24" s="7"/>
     </row>
     <row r="25" ht="32" customHeight="1" spans="1:10">
@@ -5776,28 +6501,28 @@
       <c r="C25" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
       <c r="J25" s="7"/>
     </row>
     <row r="26" ht="102" customHeight="1" spans="1:11">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="32"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="29">

--- a/固件/IP2366固件/IP2366_I2C_140W_2M50_REG.xlsx
+++ b/固件/IP2366固件/IP2366_I2C_140W_2M50_REG.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="15420" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="15420"/>
   </bookViews>
   <sheets>
     <sheet name="可读写配置寄存器" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="208">
   <si>
     <t>寄存器名称</t>
   </si>
@@ -736,14 +736,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>VRecharge[1:0]</t>
     </r>
     <r>
@@ -1045,14 +1037,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>TYPEC_MAX_POWER[2:0]</t>
     </r>
     <r>
@@ -1085,6 +1069,43 @@
         <scheme val="minor"/>
       </rPr>
       <t>）
+0：30W       1：45W
+2：60W       3：65W
+4：100W       5：140W</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EN_Snk_Pset
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>该bit设置输入充电功率是否独立设置。
+0：输入充电功率由TYPEC_MAX_POWER[2:0]设置。
+1：由SNK_POWER[2:0]设置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>TYPEC_SNK_POWER[2:0]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+设置系统的Type-C接口在输入充电模式下尝试协商的最大功率（实际输入功率取决于设备的上限，若设置功率小于140W则系统将会关闭EPR握手。若En_Snk_Pset=0则该寄存器无效）
 0：30W       1：45W
 2：60W       3：65W
 4：100W       5：140W</t>
@@ -1152,14 +1173,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>TYPEC_CC_MODE[1:0]</t>
     </r>
     <r>
@@ -1171,28 +1184,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-设置芯片C口的CC引脚对外报告的设备类型是作为输入/双向还是输出设备(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>进入仅对外输出模式时要求系统处于对外放电模式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)
-0和1: 断开连接 2：仅对外输出 3：双向口(支持输入输出)</t>
+设置芯片C口的CC引脚对外报告的设备类型是作为输入/双向还是输出设备，以及断开C口连接
+0: 仅支持输入 1：仅对外输出 2：断开CC连接 3：双向口(支持输入输出，带TrySrc)</t>
     </r>
   </si>
   <si>
@@ -1903,14 +1896,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">IP2366 2M50 140W 3S Special Firmware Register Map
 Created By: </t>
     </r>
@@ -1931,7 +1916,7 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>JUL-09-2025 16:13 For Reference Only,</t>
+      <t>SEP-19-2025 13:19 For Reference Only,</t>
     </r>
     <r>
       <rPr>
@@ -2247,6 +2232,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Vsys_OCP
 </t>
     </r>
@@ -2297,6 +2290,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Vsys_SCP
 </t>
     </r>
@@ -3696,6 +3697,48 @@
       </rPr>
       <t xml:space="preserve">
 该寄存器以ASCII码的形式返回固件编译时留下的唯一时间戳的第5个字母。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">IP2366 2M50 140W 3S Special Firmware Register Map
+Created By: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Blackadder ITC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">Redstoner_35
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>JUL-09-2025 16:13 For Reference Only,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>NOT APPLY TO OTHER VERSIONS OF Firmware!</t>
     </r>
   </si>
 </sst>
@@ -3709,7 +3752,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3765,6 +3808,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3914,16 +3965,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFF00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3937,21 +4008,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3973,13 +4031,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -4494,137 +4545,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4733,6 +4784,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4783,6 +4843,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5192,10 +5255,10 @@
       <c r="H2" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="54" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="52" t="s">
+      <c r="J2" s="55" t="s">
         <v>21</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -5372,7 +5435,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" ht="106" customHeight="1" spans="1:11">
+    <row r="10" ht="118" customHeight="1" spans="1:11">
       <c r="A10" s="2" t="s">
         <v>57</v>
       </c>
@@ -5384,23 +5447,27 @@
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="4"/>
+      <c r="G10" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
       <c r="K10" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" ht="136" customHeight="1" spans="1:11">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>20</v>
@@ -5409,24 +5476,24 @@
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
+      <c r="H11" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="57"/>
+      <c r="J11" s="58"/>
       <c r="K11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" ht="86" customHeight="1" spans="1:11">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="3" t="s">
@@ -5438,39 +5505,39 @@
       <c r="I12" s="8"/>
       <c r="J12" s="4"/>
       <c r="K12" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1" spans="1:11">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>46</v>
@@ -5478,13 +5545,13 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:11">
       <c r="A14" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -5494,18 +5561,18 @@
       <c r="I14" s="20"/>
       <c r="J14" s="7"/>
       <c r="K14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" ht="29" customHeight="1" spans="1:11">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -5515,18 +5582,18 @@
       <c r="I15" s="20"/>
       <c r="J15" s="7"/>
       <c r="K15" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:11">
       <c r="A16" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
@@ -5536,18 +5603,18 @@
       <c r="I16" s="20"/>
       <c r="J16" s="7"/>
       <c r="K16" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" ht="31" customHeight="1" spans="1:11">
       <c r="A17" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -5557,18 +5624,18 @@
       <c r="I17" s="20"/>
       <c r="J17" s="7"/>
       <c r="K17" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" ht="31" customHeight="1" spans="1:11">
       <c r="A18" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20"/>
@@ -5578,68 +5645,68 @@
       <c r="I18" s="20"/>
       <c r="J18" s="7"/>
       <c r="K18" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" ht="79" customHeight="1" spans="1:11">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="38" t="s">
+      <c r="D19" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="E19" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="H19" s="38" t="s">
+      <c r="F19" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="38" t="s">
+      <c r="G19" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="J19" s="55" t="s">
+      <c r="H19" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="59" t="s">
         <v>20</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" ht="125" customHeight="1" spans="1:11">
       <c r="A20" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="H20" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" s="38" t="s">
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="44"/>
+      <c r="G20" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="J20" s="38" t="s">
+      <c r="H20" s="41" t="s">
         <v>108</v>
+      </c>
+      <c r="I20" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" s="41" t="s">
+        <v>110</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>13</v>
@@ -5647,298 +5714,298 @@
     </row>
     <row r="21" ht="46" customHeight="1" spans="1:11">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="C21" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="56"/>
+      <c r="D21" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="60"/>
       <c r="K21" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1" spans="1:11">
-      <c r="A22" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="B22" s="45" t="s">
+      <c r="A22" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="61"/>
+      <c r="K22" s="48" t="s">
         <v>114</v>
-      </c>
-      <c r="C22" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="45" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="23" ht="115" customHeight="1" spans="1:11">
-      <c r="A23" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="58"/>
+      <c r="A23" s="51" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="62"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="50"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="50"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="50"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="53"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="53"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="50"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="53"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="50"/>
-      <c r="J26" s="50"/>
-      <c r="K26" s="50"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="53"/>
+      <c r="C26" s="53"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="50"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="53"/>
+      <c r="E28" s="53"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="53"/>
+      <c r="H28" s="53"/>
+      <c r="I28" s="53"/>
+      <c r="J28" s="53"/>
+      <c r="K28" s="53"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="50"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="53"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="53"/>
+      <c r="K29" s="53"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="50"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="53"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="50"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="53"/>
+      <c r="J31" s="53"/>
+      <c r="K31" s="53"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="50"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="53"/>
+      <c r="I33" s="53"/>
+      <c r="J33" s="53"/>
+      <c r="K33" s="53"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="50"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="50"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="50"/>
-      <c r="J36" s="50"/>
-      <c r="K36" s="50"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
+      <c r="I36" s="53"/>
+      <c r="J36" s="53"/>
+      <c r="K36" s="53"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+      <c r="J37" s="53"/>
+      <c r="K37" s="53"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
+      <c r="J38" s="53"/>
+      <c r="K38" s="53"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="53"/>
+      <c r="I39" s="53"/>
+      <c r="J39" s="53"/>
+      <c r="K39" s="53"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="53"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="50"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+      <c r="J41" s="53"/>
+      <c r="K41" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -5953,7 +6020,7 @@
     <mergeCell ref="F8:J8"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="C10:E10"/>
-    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="H10:J10"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="H11:J11"/>
     <mergeCell ref="C12:D12"/>
@@ -6030,42 +6097,42 @@
     </row>
     <row r="2" ht="97" customHeight="1" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>20</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I2" s="20"/>
       <c r="J2" s="7"/>
       <c r="L2" s="24" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" ht="64" customHeight="1" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="3" t="s">
@@ -6079,16 +6146,16 @@
     </row>
     <row r="4" ht="102" customHeight="1" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>20</v>
@@ -6096,27 +6163,27 @@
       <c r="F4" s="11"/>
       <c r="G4" s="12"/>
       <c r="H4" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="26"/>
     </row>
     <row r="5" ht="119" customHeight="1" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>20</v>
@@ -6127,28 +6194,28 @@
     </row>
     <row r="6" ht="90" customHeight="1" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F6" s="18" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>20</v>
@@ -6157,10 +6224,10 @@
     </row>
     <row r="7" ht="78" customHeight="1" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>20</v>
@@ -6168,30 +6235,30 @@
       <c r="D7" s="8"/>
       <c r="E7" s="4"/>
       <c r="F7" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D8" s="20"/>
       <c r="E8" s="20"/>
@@ -6203,13 +6270,13 @@
     </row>
     <row r="9" ht="60" customHeight="1" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D9" s="20"/>
       <c r="E9" s="20"/>
@@ -6221,13 +6288,13 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20"/>
@@ -6239,13 +6306,13 @@
     </row>
     <row r="11" ht="60" customHeight="1" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D11" s="20"/>
       <c r="E11" s="20"/>
@@ -6257,13 +6324,13 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -6275,13 +6342,13 @@
     </row>
     <row r="13" ht="76" customHeight="1" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D13" s="20"/>
       <c r="E13" s="20"/>
@@ -6293,13 +6360,13 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
@@ -6311,13 +6378,13 @@
     </row>
     <row r="15" ht="76" customHeight="1" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
@@ -6329,13 +6396,13 @@
     </row>
     <row r="16" ht="31" customHeight="1" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
@@ -6347,13 +6414,13 @@
     </row>
     <row r="17" ht="80" customHeight="1" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D17" s="20"/>
       <c r="E17" s="20"/>
@@ -6365,13 +6432,13 @@
     </row>
     <row r="18" ht="86.4" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>20</v>
@@ -6385,13 +6452,13 @@
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D19" s="20"/>
       <c r="E19" s="20"/>
@@ -6403,13 +6470,13 @@
     </row>
     <row r="20" ht="65" customHeight="1" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20"/>
@@ -6421,13 +6488,13 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D21" s="20"/>
       <c r="E21" s="20"/>
@@ -6439,13 +6506,13 @@
     </row>
     <row r="22" ht="29" customHeight="1" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D22" s="20"/>
       <c r="E22" s="20"/>
@@ -6457,13 +6524,13 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D23" s="21"/>
       <c r="E23" s="21"/>
@@ -6475,13 +6542,13 @@
     </row>
     <row r="24" ht="37" customHeight="1" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="20"/>
@@ -6493,13 +6560,13 @@
     </row>
     <row r="25" ht="32" customHeight="1" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D25" s="20"/>
       <c r="E25" s="20"/>
@@ -6511,7 +6578,7 @@
     </row>
     <row r="26" ht="102" customHeight="1" spans="1:11">
       <c r="A26" s="22" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
